--- a/artfynd/A 44424-2025 artfynd.xlsx
+++ b/artfynd/A 44424-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1365,6 +1365,1398 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129021302</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91809</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>658</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Brännan, Brännan, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>602796</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7022069</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129019176</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91513</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Brännan, Brännan, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>602836</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7022108</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129016760</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Brännan, Brännan, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>602842</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7022184</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Årsfärska ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129021329</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Brännan, Brännan, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>602797</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7022069</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129021297</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91967</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Brännan, Brännan, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>602796</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7022069</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129018626</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98643</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Brännan, Brännan, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>602811</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7022105</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129019872</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91809</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>658</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Brännan, Brännan, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>602836</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7022075</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129021307</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91513</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Brännan, Brännan, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>602797</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7022069</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129017054</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91513</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Brännan, Brännan, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>602817</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7022145</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129033779</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91809</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>658</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gåsnäs, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>602777</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7022087</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129020017</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91513</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Brännan, Brännan, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>602825</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7022067</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129033773</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gåsnäs, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>602820</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7022069</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129021286</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91509</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Brännan, Brännan, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>602796</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7022068</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129033772</v>
+      </c>
+      <c r="B21" t="n">
+        <v>12559</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>101692</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Större barkplattbagge</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pytho kolwensis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sahlberg, 1833</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gåsnäs, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>602804</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7021924</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Larv under bark på grov granlåga. Skogen avverkningsanmäld</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad, Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44424-2025 artfynd.xlsx
+++ b/artfynd/A 44424-2025 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>129021302</v>
       </c>
       <c r="B8" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129019176</v>
+        <v>129016760</v>
       </c>
       <c r="B9" t="n">
-        <v>91520</v>
+        <v>57723</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,34 +1475,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602836</v>
+        <v>602842</v>
       </c>
       <c r="R9" t="n">
-        <v>7022108</v>
+        <v>7022184</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1535,6 +1540,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Årsfärska ringhack, gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129016760</v>
+        <v>129019176</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>91523</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,39 +1582,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602842</v>
+        <v>602836</v>
       </c>
       <c r="R10" t="n">
-        <v>7022184</v>
+        <v>7022108</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1637,11 +1642,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Årsfärska ringhack, gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129018626</v>
+        <v>129021297</v>
       </c>
       <c r="B12" t="n">
-        <v>98651</v>
+        <v>91978</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,38 +1781,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>602811</v>
+        <v>602796</v>
       </c>
       <c r="R12" t="n">
-        <v>7022105</v>
+        <v>7022069</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1871,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129021297</v>
+        <v>129018626</v>
       </c>
       <c r="B13" t="n">
-        <v>91975</v>
+        <v>98656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,34 +1878,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>602796</v>
+        <v>602811</v>
       </c>
       <c r="R13" t="n">
-        <v>7022069</v>
+        <v>7022105</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1971,7 +1971,7 @@
         <v>129019872</v>
       </c>
       <c r="B14" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>129021307</v>
       </c>
       <c r="B15" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>129017054</v>
       </c>
       <c r="B16" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>129033779</v>
       </c>
       <c r="B17" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>129020017</v>
       </c>
       <c r="B18" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>129021286</v>
       </c>
       <c r="B20" t="n">
-        <v>91516</v>
+        <v>91519</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 44424-2025 artfynd.xlsx
+++ b/artfynd/A 44424-2025 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>129021302</v>
       </c>
       <c r="B8" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129016760</v>
+        <v>129019176</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,39 +1475,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602842</v>
+        <v>602836</v>
       </c>
       <c r="R9" t="n">
-        <v>7022184</v>
+        <v>7022108</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1540,11 +1535,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Årsfärska ringhack, gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129019176</v>
+        <v>129016760</v>
       </c>
       <c r="B10" t="n">
-        <v>91523</v>
+        <v>57723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,34 +1572,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602836</v>
+        <v>602842</v>
       </c>
       <c r="R10" t="n">
-        <v>7022108</v>
+        <v>7022184</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1642,6 +1637,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Årsfärska ringhack, gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1773,7 +1773,7 @@
         <v>129021297</v>
       </c>
       <c r="B12" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>129018626</v>
       </c>
       <c r="B13" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>129019872</v>
       </c>
       <c r="B14" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>129021307</v>
       </c>
       <c r="B15" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>129017054</v>
       </c>
       <c r="B16" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>129033779</v>
       </c>
       <c r="B17" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>129020017</v>
       </c>
       <c r="B18" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>129021286</v>
       </c>
       <c r="B20" t="n">
-        <v>91519</v>
+        <v>91522</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 44424-2025 artfynd.xlsx
+++ b/artfynd/A 44424-2025 artfynd.xlsx
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129019176</v>
+        <v>129016760</v>
       </c>
       <c r="B9" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,34 +1475,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602836</v>
+        <v>602842</v>
       </c>
       <c r="R9" t="n">
-        <v>7022108</v>
+        <v>7022184</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1535,6 +1540,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Årsfärska ringhack, gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129016760</v>
+        <v>129019176</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,39 +1582,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602842</v>
+        <v>602836</v>
       </c>
       <c r="R10" t="n">
-        <v>7022184</v>
+        <v>7022108</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1637,11 +1642,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Årsfärska ringhack, gran</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 44424-2025 artfynd.xlsx
+++ b/artfynd/A 44424-2025 artfynd.xlsx
@@ -2162,10 +2162,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129017054</v>
+        <v>129033779</v>
       </c>
       <c r="B16" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2173,37 +2173,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Ång</t>
+          <t>Gåsnäs, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>602817</v>
+        <v>602777</v>
       </c>
       <c r="R16" t="n">
-        <v>7022145</v>
+        <v>7022087</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2247,22 +2247,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129033779</v>
+        <v>129017054</v>
       </c>
       <c r="B17" t="n">
-        <v>91811</v>
+        <v>91526</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2270,37 +2270,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gåsnäs, Ång</t>
+          <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>602777</v>
+        <v>602817</v>
       </c>
       <c r="R17" t="n">
-        <v>7022087</v>
+        <v>7022145</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2344,12 +2344,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 44424-2025 artfynd.xlsx
+++ b/artfynd/A 44424-2025 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>129021302</v>
       </c>
       <c r="B8" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129016760</v>
+        <v>129019176</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>91533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,39 +1475,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602842</v>
+        <v>602836</v>
       </c>
       <c r="R9" t="n">
-        <v>7022184</v>
+        <v>7022108</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1540,11 +1535,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Årsfärska ringhack, gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129019176</v>
+        <v>129016760</v>
       </c>
       <c r="B10" t="n">
-        <v>91526</v>
+        <v>57725</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,34 +1572,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602836</v>
+        <v>602842</v>
       </c>
       <c r="R10" t="n">
-        <v>7022108</v>
+        <v>7022184</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1642,6 +1637,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Årsfärska ringhack, gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,7 +1671,7 @@
         <v>129021329</v>
       </c>
       <c r="B11" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>129021297</v>
       </c>
       <c r="B12" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>129018626</v>
       </c>
       <c r="B13" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>129019872</v>
       </c>
       <c r="B14" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>129021307</v>
       </c>
       <c r="B15" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>129033779</v>
       </c>
       <c r="B16" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>129017054</v>
       </c>
       <c r="B17" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>129020017</v>
       </c>
       <c r="B18" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>129033773</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2550,48 +2550,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129021286</v>
+        <v>129033772</v>
       </c>
       <c r="B20" t="n">
-        <v>91522</v>
+        <v>12559</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>101692</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Större barkplattbagge</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pytho kolwensis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Sahlberg, 1833</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Ång</t>
+          <t>Gåsnäs, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>602796</v>
+        <v>602804</v>
       </c>
       <c r="R20" t="n">
-        <v>7022068</v>
+        <v>7021924</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2623,81 +2632,78 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Larv under bark på grov granlåga. Skogen avverkningsanmäld</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad, Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129033772</v>
+        <v>129021286</v>
       </c>
       <c r="B21" t="n">
-        <v>12559</v>
+        <v>91529</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>101692</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Större barkplattbagge</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pytho kolwensis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sahlberg, 1833</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gåsnäs, Ång</t>
+          <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>602804</v>
+        <v>602796</v>
       </c>
       <c r="R21" t="n">
-        <v>7021924</v>
+        <v>7022068</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2729,30 +2735,24 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Larv under bark på grov granlåga. Skogen avverkningsanmäld</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Daniel Rutschman</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 44424-2025 artfynd.xlsx
+++ b/artfynd/A 44424-2025 artfynd.xlsx
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129019176</v>
+        <v>129016760</v>
       </c>
       <c r="B9" t="n">
-        <v>91533</v>
+        <v>57725</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,34 +1475,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602836</v>
+        <v>602842</v>
       </c>
       <c r="R9" t="n">
-        <v>7022108</v>
+        <v>7022184</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1535,6 +1540,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Årsfärska ringhack, gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129016760</v>
+        <v>129019176</v>
       </c>
       <c r="B10" t="n">
-        <v>57725</v>
+        <v>91533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,39 +1582,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602842</v>
+        <v>602836</v>
       </c>
       <c r="R10" t="n">
-        <v>7022184</v>
+        <v>7022108</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1637,11 +1642,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Årsfärska ringhack, gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2162,10 +2162,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129033779</v>
+        <v>129017054</v>
       </c>
       <c r="B16" t="n">
-        <v>91818</v>
+        <v>91533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2173,37 +2173,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gåsnäs, Ång</t>
+          <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>602777</v>
+        <v>602817</v>
       </c>
       <c r="R16" t="n">
-        <v>7022087</v>
+        <v>7022145</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2247,22 +2247,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129017054</v>
+        <v>129033779</v>
       </c>
       <c r="B17" t="n">
-        <v>91533</v>
+        <v>91818</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2270,37 +2270,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Ång</t>
+          <t>Gåsnäs, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>602817</v>
+        <v>602777</v>
       </c>
       <c r="R17" t="n">
-        <v>7022145</v>
+        <v>7022087</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2344,12 +2344,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 44424-2025 artfynd.xlsx
+++ b/artfynd/A 44424-2025 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>129021302</v>
       </c>
       <c r="B8" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>129019176</v>
       </c>
       <c r="B10" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129021297</v>
+        <v>129018626</v>
       </c>
       <c r="B12" t="n">
-        <v>91988</v>
+        <v>98676</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,34 +1781,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>602796</v>
+        <v>602811</v>
       </c>
       <c r="R12" t="n">
-        <v>7022069</v>
+        <v>7022105</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1867,10 +1871,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129018626</v>
+        <v>129021297</v>
       </c>
       <c r="B13" t="n">
-        <v>98669</v>
+        <v>91995</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,38 +1882,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>602811</v>
+        <v>602796</v>
       </c>
       <c r="R13" t="n">
-        <v>7022105</v>
+        <v>7022069</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1971,7 +1971,7 @@
         <v>129019872</v>
       </c>
       <c r="B14" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>129021307</v>
       </c>
       <c r="B15" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>129017054</v>
       </c>
       <c r="B16" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>129033779</v>
       </c>
       <c r="B17" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2356,10 +2356,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129020017</v>
+        <v>129033773</v>
       </c>
       <c r="B18" t="n">
-        <v>91533</v>
+        <v>57722</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2367,37 +2367,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Ång</t>
+          <t>Gåsnäs, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>602825</v>
+        <v>602820</v>
       </c>
       <c r="R18" t="n">
-        <v>7022067</v>
+        <v>7022069</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2441,22 +2441,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129033773</v>
+        <v>129020017</v>
       </c>
       <c r="B19" t="n">
-        <v>57722</v>
+        <v>91540</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2464,37 +2464,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gåsnäs, Ång</t>
+          <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>602820</v>
+        <v>602825</v>
       </c>
       <c r="R19" t="n">
-        <v>7022069</v>
+        <v>7022067</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2538,69 +2538,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129033772</v>
+        <v>129021286</v>
       </c>
       <c r="B20" t="n">
-        <v>12559</v>
+        <v>91536</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>101692</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Större barkplattbagge</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pytho kolwensis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sahlberg, 1833</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gåsnäs, Ång</t>
+          <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>602804</v>
+        <v>602796</v>
       </c>
       <c r="R20" t="n">
-        <v>7021924</v>
+        <v>7022068</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2632,78 +2623,81 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Larv under bark på grov granlåga. Skogen avverkningsanmäld</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Daniel Rutschman</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129021286</v>
+        <v>129033772</v>
       </c>
       <c r="B21" t="n">
-        <v>91529</v>
+        <v>12559</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>101692</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Större barkplattbagge</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pytho kolwensis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Sahlberg, 1833</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Ång</t>
+          <t>Gåsnäs, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>602796</v>
+        <v>602804</v>
       </c>
       <c r="R21" t="n">
-        <v>7022068</v>
+        <v>7021924</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2735,24 +2729,30 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Larv under bark på grov granlåga. Skogen avverkningsanmäld</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad, Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 44424-2025 artfynd.xlsx
+++ b/artfynd/A 44424-2025 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>129021302</v>
       </c>
       <c r="B8" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129016760</v>
+        <v>129019176</v>
       </c>
       <c r="B9" t="n">
-        <v>57725</v>
+        <v>91542</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,39 +1475,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602842</v>
+        <v>602836</v>
       </c>
       <c r="R9" t="n">
-        <v>7022184</v>
+        <v>7022108</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1540,11 +1535,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Årsfärska ringhack, gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129019176</v>
+        <v>129016760</v>
       </c>
       <c r="B10" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,34 +1572,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602836</v>
+        <v>602842</v>
       </c>
       <c r="R10" t="n">
-        <v>7022108</v>
+        <v>7022184</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1642,6 +1637,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Årsfärska ringhack, gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,7 +1671,7 @@
         <v>129021329</v>
       </c>
       <c r="B11" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129018626</v>
+        <v>129021297</v>
       </c>
       <c r="B12" t="n">
-        <v>98676</v>
+        <v>91997</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,38 +1781,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>602811</v>
+        <v>602796</v>
       </c>
       <c r="R12" t="n">
-        <v>7022105</v>
+        <v>7022069</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1871,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129021297</v>
+        <v>129018626</v>
       </c>
       <c r="B13" t="n">
-        <v>91995</v>
+        <v>98678</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,34 +1878,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>602796</v>
+        <v>602811</v>
       </c>
       <c r="R13" t="n">
-        <v>7022069</v>
+        <v>7022105</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1971,7 +1971,7 @@
         <v>129019872</v>
       </c>
       <c r="B14" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>129021307</v>
       </c>
       <c r="B15" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>129017054</v>
       </c>
       <c r="B16" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>129033779</v>
       </c>
       <c r="B17" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2356,10 +2356,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129033773</v>
+        <v>129020017</v>
       </c>
       <c r="B18" t="n">
-        <v>57722</v>
+        <v>91542</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2367,37 +2367,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gåsnäs, Ång</t>
+          <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>602820</v>
+        <v>602825</v>
       </c>
       <c r="R18" t="n">
-        <v>7022069</v>
+        <v>7022067</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2441,22 +2441,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129020017</v>
+        <v>129033773</v>
       </c>
       <c r="B19" t="n">
-        <v>91540</v>
+        <v>57724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2464,37 +2464,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Ång</t>
+          <t>Gåsnäs, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>602825</v>
+        <v>602820</v>
       </c>
       <c r="R19" t="n">
-        <v>7022067</v>
+        <v>7022069</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2538,60 +2538,69 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129021286</v>
+        <v>129033772</v>
       </c>
       <c r="B20" t="n">
-        <v>91536</v>
+        <v>12559</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>101692</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Större barkplattbagge</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pytho kolwensis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Sahlberg, 1833</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Ång</t>
+          <t>Gåsnäs, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>602796</v>
+        <v>602804</v>
       </c>
       <c r="R20" t="n">
-        <v>7022068</v>
+        <v>7021924</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2623,81 +2632,78 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Larv under bark på grov granlåga. Skogen avverkningsanmäld</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad, Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129033772</v>
+        <v>129021286</v>
       </c>
       <c r="B21" t="n">
-        <v>12559</v>
+        <v>91538</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>101692</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Större barkplattbagge</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pytho kolwensis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sahlberg, 1833</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gåsnäs, Ång</t>
+          <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>602804</v>
+        <v>602796</v>
       </c>
       <c r="R21" t="n">
-        <v>7021924</v>
+        <v>7022068</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2729,30 +2735,24 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Larv under bark på grov granlåga. Skogen avverkningsanmäld</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Daniel Rutschman</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 44424-2025 artfynd.xlsx
+++ b/artfynd/A 44424-2025 artfynd.xlsx
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129019176</v>
+        <v>129016760</v>
       </c>
       <c r="B9" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,34 +1475,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602836</v>
+        <v>602842</v>
       </c>
       <c r="R9" t="n">
-        <v>7022108</v>
+        <v>7022184</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1535,6 +1540,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Årsfärska ringhack, gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129016760</v>
+        <v>129019176</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>91542</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,39 +1582,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602842</v>
+        <v>602836</v>
       </c>
       <c r="R10" t="n">
-        <v>7022184</v>
+        <v>7022108</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1637,11 +1642,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Årsfärska ringhack, gran</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 44424-2025 artfynd.xlsx
+++ b/artfynd/A 44424-2025 artfynd.xlsx
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129021297</v>
+        <v>129018626</v>
       </c>
       <c r="B12" t="n">
-        <v>91997</v>
+        <v>98678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,34 +1781,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>602796</v>
+        <v>602811</v>
       </c>
       <c r="R12" t="n">
-        <v>7022069</v>
+        <v>7022105</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1867,10 +1871,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129018626</v>
+        <v>129021297</v>
       </c>
       <c r="B13" t="n">
-        <v>98678</v>
+        <v>91997</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,38 +1882,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>602811</v>
+        <v>602796</v>
       </c>
       <c r="R13" t="n">
-        <v>7022105</v>
+        <v>7022069</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 44424-2025 artfynd.xlsx
+++ b/artfynd/A 44424-2025 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>129021302</v>
       </c>
       <c r="B8" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129016760</v>
+        <v>129019176</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,39 +1475,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602842</v>
+        <v>602836</v>
       </c>
       <c r="R9" t="n">
-        <v>7022184</v>
+        <v>7022108</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1540,11 +1535,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Årsfärska ringhack, gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129019176</v>
+        <v>129016760</v>
       </c>
       <c r="B10" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,34 +1572,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602836</v>
+        <v>602842</v>
       </c>
       <c r="R10" t="n">
-        <v>7022108</v>
+        <v>7022184</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1642,6 +1637,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Årsfärska ringhack, gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129018626</v>
+        <v>129021297</v>
       </c>
       <c r="B12" t="n">
-        <v>98678</v>
+        <v>91992</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,38 +1781,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>602811</v>
+        <v>602796</v>
       </c>
       <c r="R12" t="n">
-        <v>7022105</v>
+        <v>7022069</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1871,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129021297</v>
+        <v>129018626</v>
       </c>
       <c r="B13" t="n">
-        <v>91997</v>
+        <v>98704</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,34 +1878,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>602796</v>
+        <v>602811</v>
       </c>
       <c r="R13" t="n">
-        <v>7022069</v>
+        <v>7022105</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1971,7 +1971,7 @@
         <v>129019872</v>
       </c>
       <c r="B14" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>129021307</v>
       </c>
       <c r="B15" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>129017054</v>
       </c>
       <c r="B16" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>129033779</v>
       </c>
       <c r="B17" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>129020017</v>
       </c>
       <c r="B18" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2550,57 +2550,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129033772</v>
+        <v>129021286</v>
       </c>
       <c r="B20" t="n">
-        <v>12559</v>
+        <v>91536</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>101692</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Större barkplattbagge</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pytho kolwensis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sahlberg, 1833</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gåsnäs, Ång</t>
+          <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>602804</v>
+        <v>602796</v>
       </c>
       <c r="R20" t="n">
-        <v>7021924</v>
+        <v>7022068</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2632,78 +2623,81 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Larv under bark på grov granlåga. Skogen avverkningsanmäld</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Daniel Rutschman</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129021286</v>
+        <v>129033772</v>
       </c>
       <c r="B21" t="n">
-        <v>91538</v>
+        <v>12559</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>101692</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Större barkplattbagge</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pytho kolwensis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Sahlberg, 1833</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Ång</t>
+          <t>Gåsnäs, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>602796</v>
+        <v>602804</v>
       </c>
       <c r="R21" t="n">
-        <v>7022068</v>
+        <v>7021924</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2735,24 +2729,30 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Larv under bark på grov granlåga. Skogen avverkningsanmäld</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad, Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 44424-2025 artfynd.xlsx
+++ b/artfynd/A 44424-2025 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>129021302</v>
       </c>
       <c r="B8" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>129021297</v>
       </c>
       <c r="B12" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>129018626</v>
       </c>
       <c r="B13" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>129019872</v>
       </c>
       <c r="B14" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>129033779</v>
       </c>
       <c r="B17" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2356,10 +2356,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129020017</v>
+        <v>129033773</v>
       </c>
       <c r="B18" t="n">
-        <v>91540</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2367,37 +2367,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Ång</t>
+          <t>Gåsnäs, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>602825</v>
+        <v>602820</v>
       </c>
       <c r="R18" t="n">
-        <v>7022067</v>
+        <v>7022069</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2441,22 +2441,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129033773</v>
+        <v>129020017</v>
       </c>
       <c r="B19" t="n">
-        <v>57724</v>
+        <v>91540</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2464,37 +2464,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gåsnäs, Ång</t>
+          <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>602820</v>
+        <v>602825</v>
       </c>
       <c r="R19" t="n">
-        <v>7022069</v>
+        <v>7022067</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2538,12 +2538,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 44424-2025 artfynd.xlsx
+++ b/artfynd/A 44424-2025 artfynd.xlsx
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129019176</v>
+        <v>129016760</v>
       </c>
       <c r="B9" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,34 +1475,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602836</v>
+        <v>602842</v>
       </c>
       <c r="R9" t="n">
-        <v>7022108</v>
+        <v>7022184</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1535,6 +1540,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Årsfärska ringhack, gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129016760</v>
+        <v>129019176</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,39 +1582,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602842</v>
+        <v>602836</v>
       </c>
       <c r="R10" t="n">
-        <v>7022184</v>
+        <v>7022108</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1637,11 +1642,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Årsfärska ringhack, gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129021297</v>
+        <v>129018626</v>
       </c>
       <c r="B12" t="n">
-        <v>91993</v>
+        <v>98706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,34 +1781,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>602796</v>
+        <v>602811</v>
       </c>
       <c r="R12" t="n">
-        <v>7022069</v>
+        <v>7022105</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1867,10 +1871,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129018626</v>
+        <v>129021297</v>
       </c>
       <c r="B13" t="n">
-        <v>98705</v>
+        <v>91993</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,38 +1882,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>602811</v>
+        <v>602796</v>
       </c>
       <c r="R13" t="n">
-        <v>7022105</v>
+        <v>7022069</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2162,10 +2162,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129017054</v>
+        <v>129033779</v>
       </c>
       <c r="B16" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2173,37 +2173,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Ång</t>
+          <t>Gåsnäs, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>602817</v>
+        <v>602777</v>
       </c>
       <c r="R16" t="n">
-        <v>7022145</v>
+        <v>7022087</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2247,22 +2247,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129033779</v>
+        <v>129017054</v>
       </c>
       <c r="B17" t="n">
-        <v>91838</v>
+        <v>91540</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2270,37 +2270,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gåsnäs, Ång</t>
+          <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>602777</v>
+        <v>602817</v>
       </c>
       <c r="R17" t="n">
-        <v>7022087</v>
+        <v>7022145</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2344,22 +2344,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129033773</v>
+        <v>129020017</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>91540</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2367,37 +2367,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gåsnäs, Ång</t>
+          <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>602820</v>
+        <v>602825</v>
       </c>
       <c r="R18" t="n">
-        <v>7022069</v>
+        <v>7022067</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2441,22 +2441,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129020017</v>
+        <v>129033773</v>
       </c>
       <c r="B19" t="n">
-        <v>91540</v>
+        <v>57724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2464,37 +2464,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Ång</t>
+          <t>Gåsnäs, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>602825</v>
+        <v>602820</v>
       </c>
       <c r="R19" t="n">
-        <v>7022067</v>
+        <v>7022069</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2538,60 +2538,69 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129021286</v>
+        <v>129033772</v>
       </c>
       <c r="B20" t="n">
-        <v>91536</v>
+        <v>12559</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>101692</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Större barkplattbagge</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pytho kolwensis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Sahlberg, 1833</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Ång</t>
+          <t>Gåsnäs, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>602796</v>
+        <v>602804</v>
       </c>
       <c r="R20" t="n">
-        <v>7022068</v>
+        <v>7021924</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2623,81 +2632,78 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Larv under bark på grov granlåga. Skogen avverkningsanmäld</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad, Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129033772</v>
+        <v>129021286</v>
       </c>
       <c r="B21" t="n">
-        <v>12559</v>
+        <v>91536</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>101692</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Större barkplattbagge</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pytho kolwensis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sahlberg, 1833</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gåsnäs, Ång</t>
+          <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>602804</v>
+        <v>602796</v>
       </c>
       <c r="R21" t="n">
-        <v>7021924</v>
+        <v>7022068</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2729,30 +2735,24 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Larv under bark på grov granlåga. Skogen avverkningsanmäld</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Daniel Rutschman</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 44424-2025 artfynd.xlsx
+++ b/artfynd/A 44424-2025 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>129021302</v>
       </c>
       <c r="B8" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>129019176</v>
       </c>
       <c r="B10" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129018626</v>
+        <v>129021297</v>
       </c>
       <c r="B12" t="n">
-        <v>98706</v>
+        <v>91996</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,38 +1781,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>602811</v>
+        <v>602796</v>
       </c>
       <c r="R12" t="n">
-        <v>7022105</v>
+        <v>7022069</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1871,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129021297</v>
+        <v>129018626</v>
       </c>
       <c r="B13" t="n">
-        <v>91993</v>
+        <v>98710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,34 +1878,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>602796</v>
+        <v>602811</v>
       </c>
       <c r="R13" t="n">
-        <v>7022069</v>
+        <v>7022105</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1971,7 +1971,7 @@
         <v>129019872</v>
       </c>
       <c r="B14" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>129021307</v>
       </c>
       <c r="B15" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,10 +2162,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129033779</v>
+        <v>129017054</v>
       </c>
       <c r="B16" t="n">
-        <v>91838</v>
+        <v>91543</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2173,37 +2173,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gåsnäs, Ång</t>
+          <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>602777</v>
+        <v>602817</v>
       </c>
       <c r="R16" t="n">
-        <v>7022087</v>
+        <v>7022145</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2247,22 +2247,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129017054</v>
+        <v>129033779</v>
       </c>
       <c r="B17" t="n">
-        <v>91540</v>
+        <v>91841</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2270,37 +2270,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Ång</t>
+          <t>Gåsnäs, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>602817</v>
+        <v>602777</v>
       </c>
       <c r="R17" t="n">
-        <v>7022145</v>
+        <v>7022087</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2344,12 +2344,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2359,7 +2359,7 @@
         <v>129020017</v>
       </c>
       <c r="B18" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2550,57 +2550,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129033772</v>
+        <v>129021286</v>
       </c>
       <c r="B20" t="n">
-        <v>12559</v>
+        <v>91539</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>101692</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Större barkplattbagge</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pytho kolwensis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sahlberg, 1833</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gåsnäs, Ång</t>
+          <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>602804</v>
+        <v>602796</v>
       </c>
       <c r="R20" t="n">
-        <v>7021924</v>
+        <v>7022068</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2632,78 +2623,81 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Larv under bark på grov granlåga. Skogen avverkningsanmäld</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Daniel Rutschman</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129021286</v>
+        <v>129033772</v>
       </c>
       <c r="B21" t="n">
-        <v>91536</v>
+        <v>12559</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>101692</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Större barkplattbagge</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pytho kolwensis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Sahlberg, 1833</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Ång</t>
+          <t>Gåsnäs, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>602796</v>
+        <v>602804</v>
       </c>
       <c r="R21" t="n">
-        <v>7022068</v>
+        <v>7021924</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2735,24 +2729,30 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Larv under bark på grov granlåga. Skogen avverkningsanmäld</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad, Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 44424-2025 artfynd.xlsx
+++ b/artfynd/A 44424-2025 artfynd.xlsx
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129016760</v>
+        <v>129019176</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>91543</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,39 +1475,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602842</v>
+        <v>602836</v>
       </c>
       <c r="R9" t="n">
-        <v>7022184</v>
+        <v>7022108</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1540,11 +1535,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Årsfärska ringhack, gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129019176</v>
+        <v>129016760</v>
       </c>
       <c r="B10" t="n">
-        <v>91543</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,34 +1572,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602836</v>
+        <v>602842</v>
       </c>
       <c r="R10" t="n">
-        <v>7022108</v>
+        <v>7022184</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1642,6 +1637,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Årsfärska ringhack, gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2356,10 +2356,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129020017</v>
+        <v>129033773</v>
       </c>
       <c r="B18" t="n">
-        <v>91543</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2367,37 +2367,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Ång</t>
+          <t>Gåsnäs, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>602825</v>
+        <v>602820</v>
       </c>
       <c r="R18" t="n">
-        <v>7022067</v>
+        <v>7022069</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2441,22 +2441,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129033773</v>
+        <v>129020017</v>
       </c>
       <c r="B19" t="n">
-        <v>57724</v>
+        <v>91543</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2464,37 +2464,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gåsnäs, Ång</t>
+          <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>602820</v>
+        <v>602825</v>
       </c>
       <c r="R19" t="n">
-        <v>7022069</v>
+        <v>7022067</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2538,12 +2538,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 44424-2025 artfynd.xlsx
+++ b/artfynd/A 44424-2025 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>129021302</v>
       </c>
       <c r="B8" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129019176</v>
+        <v>129016760</v>
       </c>
       <c r="B9" t="n">
-        <v>91543</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,34 +1475,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602836</v>
+        <v>602842</v>
       </c>
       <c r="R9" t="n">
-        <v>7022108</v>
+        <v>7022184</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1535,6 +1540,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Årsfärska ringhack, gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129016760</v>
+        <v>129019176</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>91545</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,39 +1582,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602842</v>
+        <v>602836</v>
       </c>
       <c r="R10" t="n">
-        <v>7022184</v>
+        <v>7022108</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1637,11 +1642,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Årsfärska ringhack, gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1773,7 +1773,7 @@
         <v>129021297</v>
       </c>
       <c r="B12" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>129018626</v>
       </c>
       <c r="B13" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>129019872</v>
       </c>
       <c r="B14" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>129021307</v>
       </c>
       <c r="B15" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>129017054</v>
       </c>
       <c r="B16" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>129033779</v>
       </c>
       <c r="B17" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2356,10 +2356,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129033773</v>
+        <v>129020017</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>91545</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2367,37 +2367,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gåsnäs, Ång</t>
+          <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>602820</v>
+        <v>602825</v>
       </c>
       <c r="R18" t="n">
-        <v>7022069</v>
+        <v>7022067</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2441,22 +2441,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129020017</v>
+        <v>129033773</v>
       </c>
       <c r="B19" t="n">
-        <v>91543</v>
+        <v>57724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2464,37 +2464,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Ång</t>
+          <t>Gåsnäs, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>602825</v>
+        <v>602820</v>
       </c>
       <c r="R19" t="n">
-        <v>7022067</v>
+        <v>7022069</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2538,60 +2538,69 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129021286</v>
+        <v>129033772</v>
       </c>
       <c r="B20" t="n">
-        <v>91539</v>
+        <v>12559</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>101692</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Större barkplattbagge</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pytho kolwensis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Sahlberg, 1833</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Ång</t>
+          <t>Gåsnäs, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>602796</v>
+        <v>602804</v>
       </c>
       <c r="R20" t="n">
-        <v>7022068</v>
+        <v>7021924</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2623,81 +2632,78 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Larv under bark på grov granlåga. Skogen avverkningsanmäld</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad, Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129033772</v>
+        <v>129021286</v>
       </c>
       <c r="B21" t="n">
-        <v>12559</v>
+        <v>91541</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>101692</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Större barkplattbagge</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pytho kolwensis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sahlberg, 1833</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gåsnäs, Ång</t>
+          <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>602804</v>
+        <v>602796</v>
       </c>
       <c r="R21" t="n">
-        <v>7021924</v>
+        <v>7022068</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2729,30 +2735,24 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Larv under bark på grov granlåga. Skogen avverkningsanmäld</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Daniel Rutschman</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 44424-2025 artfynd.xlsx
+++ b/artfynd/A 44424-2025 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>129021302</v>
       </c>
       <c r="B8" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129016760</v>
+        <v>129019176</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,39 +1475,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602842</v>
+        <v>602836</v>
       </c>
       <c r="R9" t="n">
-        <v>7022184</v>
+        <v>7022108</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1540,11 +1535,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Årsfärska ringhack, gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129019176</v>
+        <v>129016760</v>
       </c>
       <c r="B10" t="n">
-        <v>91545</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,34 +1572,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602836</v>
+        <v>602842</v>
       </c>
       <c r="R10" t="n">
-        <v>7022108</v>
+        <v>7022184</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1642,6 +1637,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Årsfärska ringhack, gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1773,7 +1773,7 @@
         <v>129021297</v>
       </c>
       <c r="B12" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>129018626</v>
       </c>
       <c r="B13" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>129019872</v>
       </c>
       <c r="B14" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>129021307</v>
       </c>
       <c r="B15" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>129017054</v>
       </c>
       <c r="B16" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>129033779</v>
       </c>
       <c r="B17" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>129020017</v>
       </c>
       <c r="B18" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2550,57 +2550,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129033772</v>
+        <v>129021286</v>
       </c>
       <c r="B20" t="n">
-        <v>12559</v>
+        <v>91545</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>101692</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Större barkplattbagge</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pytho kolwensis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sahlberg, 1833</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gåsnäs, Ång</t>
+          <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>602804</v>
+        <v>602796</v>
       </c>
       <c r="R20" t="n">
-        <v>7021924</v>
+        <v>7022068</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2632,78 +2623,81 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Larv under bark på grov granlåga. Skogen avverkningsanmäld</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Daniel Rutschman</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129021286</v>
+        <v>129033772</v>
       </c>
       <c r="B21" t="n">
-        <v>91541</v>
+        <v>12559</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>101692</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Större barkplattbagge</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pytho kolwensis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Sahlberg, 1833</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Ång</t>
+          <t>Gåsnäs, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>602796</v>
+        <v>602804</v>
       </c>
       <c r="R21" t="n">
-        <v>7022068</v>
+        <v>7021924</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2735,24 +2729,30 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Larv under bark på grov granlåga. Skogen avverkningsanmäld</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad, Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 44424-2025 artfynd.xlsx
+++ b/artfynd/A 44424-2025 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>129021302</v>
       </c>
       <c r="B8" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>129019176</v>
       </c>
       <c r="B9" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>129021297</v>
       </c>
       <c r="B12" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>129018626</v>
       </c>
       <c r="B13" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>129019872</v>
       </c>
       <c r="B14" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>129021307</v>
       </c>
       <c r="B15" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>129017054</v>
       </c>
       <c r="B16" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>129033779</v>
       </c>
       <c r="B17" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>129020017</v>
       </c>
       <c r="B18" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>129021286</v>
       </c>
       <c r="B20" t="n">
-        <v>91545</v>
+        <v>91546</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 44424-2025 artfynd.xlsx
+++ b/artfynd/A 44424-2025 artfynd.xlsx
@@ -2356,10 +2356,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129020017</v>
+        <v>129033773</v>
       </c>
       <c r="B18" t="n">
-        <v>91550</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2367,37 +2367,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Ång</t>
+          <t>Gåsnäs, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>602825</v>
+        <v>602820</v>
       </c>
       <c r="R18" t="n">
-        <v>7022067</v>
+        <v>7022069</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2441,22 +2441,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129033773</v>
+        <v>129020017</v>
       </c>
       <c r="B19" t="n">
-        <v>57724</v>
+        <v>91550</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2464,37 +2464,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gåsnäs, Ång</t>
+          <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>602820</v>
+        <v>602825</v>
       </c>
       <c r="R19" t="n">
-        <v>7022069</v>
+        <v>7022067</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2538,12 +2538,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 44424-2025 artfynd.xlsx
+++ b/artfynd/A 44424-2025 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>129021302</v>
       </c>
       <c r="B8" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129019176</v>
+        <v>129016760</v>
       </c>
       <c r="B9" t="n">
-        <v>91550</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,34 +1475,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602836</v>
+        <v>602842</v>
       </c>
       <c r="R9" t="n">
-        <v>7022108</v>
+        <v>7022184</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1535,6 +1540,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Årsfärska ringhack, gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129016760</v>
+        <v>129019176</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,39 +1582,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602842</v>
+        <v>602836</v>
       </c>
       <c r="R10" t="n">
-        <v>7022184</v>
+        <v>7022108</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1637,11 +1642,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Årsfärska ringhack, gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1773,7 +1773,7 @@
         <v>129021297</v>
       </c>
       <c r="B12" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>129018626</v>
       </c>
       <c r="B13" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>129019872</v>
       </c>
       <c r="B14" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>129021307</v>
       </c>
       <c r="B15" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>129017054</v>
       </c>
       <c r="B16" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>129033779</v>
       </c>
       <c r="B17" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2356,10 +2356,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129033773</v>
+        <v>129020017</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>91553</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2367,37 +2367,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gåsnäs, Ång</t>
+          <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>602820</v>
+        <v>602825</v>
       </c>
       <c r="R18" t="n">
-        <v>7022069</v>
+        <v>7022067</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2441,22 +2441,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129020017</v>
+        <v>129033773</v>
       </c>
       <c r="B19" t="n">
-        <v>91550</v>
+        <v>57724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2464,37 +2464,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Ång</t>
+          <t>Gåsnäs, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>602825</v>
+        <v>602820</v>
       </c>
       <c r="R19" t="n">
-        <v>7022067</v>
+        <v>7022069</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2538,12 +2538,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2553,7 +2553,7 @@
         <v>129021286</v>
       </c>
       <c r="B20" t="n">
-        <v>91546</v>
+        <v>91549</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 44424-2025 artfynd.xlsx
+++ b/artfynd/A 44424-2025 artfynd.xlsx
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129016760</v>
+        <v>129019176</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,39 +1475,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602842</v>
+        <v>602836</v>
       </c>
       <c r="R9" t="n">
-        <v>7022184</v>
+        <v>7022108</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1540,11 +1535,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Årsfärska ringhack, gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129019176</v>
+        <v>129016760</v>
       </c>
       <c r="B10" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,34 +1572,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602836</v>
+        <v>602842</v>
       </c>
       <c r="R10" t="n">
-        <v>7022108</v>
+        <v>7022184</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1642,6 +1637,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Årsfärska ringhack, gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2550,48 +2550,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129021286</v>
+        <v>129033772</v>
       </c>
       <c r="B20" t="n">
-        <v>91549</v>
+        <v>12559</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>101692</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Större barkplattbagge</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pytho kolwensis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Sahlberg, 1833</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Ång</t>
+          <t>Gåsnäs, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>602796</v>
+        <v>602804</v>
       </c>
       <c r="R20" t="n">
-        <v>7022068</v>
+        <v>7021924</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2623,81 +2632,78 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Larv under bark på grov granlåga. Skogen avverkningsanmäld</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad, Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129033772</v>
+        <v>129021286</v>
       </c>
       <c r="B21" t="n">
-        <v>12559</v>
+        <v>91549</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>101692</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Större barkplattbagge</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pytho kolwensis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sahlberg, 1833</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gåsnäs, Ång</t>
+          <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>602804</v>
+        <v>602796</v>
       </c>
       <c r="R21" t="n">
-        <v>7021924</v>
+        <v>7022068</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2729,30 +2735,24 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Larv under bark på grov granlåga. Skogen avverkningsanmäld</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Daniel Rutschman</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
